--- a/data/trans_orig/P79A1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P79A1_2023-Habitat-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>929</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,27 +1068,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1103,27 +1103,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11038</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>7729</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13264</t>
+          <t>14689</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>633</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>660</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>7620</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,65%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>15349</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>15349</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>15349</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18021</t>
+          <t>18891</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9916</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1824,27 +1824,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>26031</t>
+          <t>27475</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22658</t>
+          <t>23830</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>28807</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18021</t>
+          <t>18891</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18021</t>
+          <t>18891</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18021</t>
+          <t>18891</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9916</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9916</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9916</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>28807</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>28807</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>28807</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>27378</t>
+          <t>30961</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22062</t>
+          <t>24631</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29989</t>
+          <t>33683</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>22604</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16686</t>
+          <t>18895</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22292</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>47651</t>
+          <t>53565</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41420</t>
+          <t>46813</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50988</t>
+          <t>57330</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8725</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
